--- a/03_Outputs/Turistica_Agroecologica/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/02_Demografia/demografia.xlsx
@@ -112,7 +112,7 @@
     <numFmt numFmtId="251" formatCode="0.00"/>
     <numFmt numFmtId="252" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,23 +122,140 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -158,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -181,76 +298,97 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="198" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="238" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,22 +714,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,7 +822,7 @@
         <v>11015</v>
       </c>
       <c r="F2" s="10">
-        <v>0.164914959875434</v>
+        <v>0.115687983783727</v>
       </c>
       <c r="G2" s="6">
         <v>2928</v>
@@ -693,7 +831,7 @@
         <v>0.265819337267363</v>
       </c>
       <c r="I2" s="14">
-        <v>0.128759894459103</v>
+        <v>0.0711525843843406</v>
       </c>
       <c r="J2" s="8">
         <v>8087</v>
@@ -702,7 +840,7 @@
         <v>0.734180662732637</v>
       </c>
       <c r="L2" s="18">
-        <v>0.183578498138564</v>
+        <v>0.149587510635937</v>
       </c>
       <c r="M2" s="20">
         <v>31.0098028250626</v>
@@ -731,7 +869,7 @@
         <v>12612</v>
       </c>
       <c r="F3" s="10">
-        <v>0.188825008983112</v>
+        <v>0.132460903448059</v>
       </c>
       <c r="G3" s="6">
         <v>2709</v>
@@ -740,7 +878,7 @@
         <v>0.214795432921028</v>
       </c>
       <c r="I3" s="14">
-        <v>0.119129287598945</v>
+        <v>0.0658307210031348</v>
       </c>
       <c r="J3" s="8">
         <v>9903</v>
@@ -749,7 +887,7 @@
         <v>0.785204567078972</v>
       </c>
       <c r="L3" s="18">
-        <v>0.22480250612912</v>
+        <v>0.183178572749806</v>
       </c>
       <c r="M3" s="20">
         <v>53.040764759006</v>
@@ -778,7 +916,7 @@
         <v>6404</v>
       </c>
       <c r="F4" s="10">
-        <v>0.0958797460773745</v>
+        <v>0.0672597229369939</v>
       </c>
       <c r="G4" s="6">
         <v>2533</v>
@@ -787,7 +925,7 @@
         <v>0.395534041224235</v>
       </c>
       <c r="I4" s="14">
-        <v>0.111389621811785</v>
+        <v>0.0615537897013438</v>
       </c>
       <c r="J4" s="8">
         <v>3871</v>
@@ -796,7 +934,7 @@
         <v>0.604465958775765</v>
       </c>
       <c r="L4" s="18">
-        <v>0.0878734223190775</v>
+        <v>0.0716029743627687</v>
       </c>
       <c r="M4" s="20">
         <v>68.496051011204</v>
@@ -825,7 +963,7 @@
         <v>5038</v>
       </c>
       <c r="F5" s="10">
-        <v>0.0754281949934124</v>
+        <v>0.0529129425603647</v>
       </c>
       <c r="G5" s="6">
         <v>2289</v>
@@ -834,7 +972,7 @@
         <v>0.454346963080588</v>
       </c>
       <c r="I5" s="14">
-        <v>0.10065963060686</v>
+        <v>0.0556244076693155</v>
       </c>
       <c r="J5" s="8">
         <v>2749</v>
@@ -843,7 +981,7 @@
         <v>0.545653036919412</v>
       </c>
       <c r="L5" s="18">
-        <v>0.0624035231090529</v>
+        <v>0.0508490251932966</v>
       </c>
       <c r="M5" s="20">
         <v>43.8663596985073</v>
@@ -872,7 +1010,7 @@
         <v>3469</v>
       </c>
       <c r="F6" s="10">
-        <v>0.0519373577673973</v>
+        <v>0.0364341003854516</v>
       </c>
       <c r="G6" s="6">
         <v>377</v>
@@ -881,7 +1019,7 @@
         <v>0.108676852118766</v>
       </c>
       <c r="I6" s="14">
-        <v>0.0165787159190853</v>
+        <v>0.00916138125440451</v>
       </c>
       <c r="J6" s="8">
         <v>3092</v>
@@ -890,7 +1028,7 @@
         <v>0.891323147881234</v>
       </c>
       <c r="L6" s="18">
-        <v>0.0701897757196041</v>
+        <v>0.0571935925418963</v>
       </c>
       <c r="M6" s="20">
         <v>39.8798926615847</v>
@@ -919,7 +1057,7 @@
         <v>9909</v>
       </c>
       <c r="F7" s="10">
-        <v>0.148356090549766</v>
+        <v>0.104071922951698</v>
       </c>
       <c r="G7" s="6">
         <v>3524</v>
@@ -928,7 +1066,7 @@
         <v>0.355636290241195</v>
       </c>
       <c r="I7" s="14">
-        <v>0.154969217238347</v>
+        <v>0.0856358290199509</v>
       </c>
       <c r="J7" s="8">
         <v>6385</v>
@@ -937,7 +1075,7 @@
         <v>0.644363709758805</v>
       </c>
       <c r="L7" s="18">
-        <v>0.144942340869881</v>
+        <v>0.118105138544634</v>
       </c>
       <c r="M7" s="20">
         <v>37.2849013664978</v>
@@ -966,7 +1104,7 @@
         <v>18345</v>
       </c>
       <c r="F8" s="10">
-        <v>0.274658641753503</v>
+        <v>0.192673269406489</v>
       </c>
       <c r="G8" s="6">
         <v>8380</v>
@@ -975,7 +1113,7 @@
         <v>0.456800218043063</v>
       </c>
       <c r="I8" s="14">
-        <v>0.368513632365875</v>
+        <v>0.203640251755729</v>
       </c>
       <c r="J8" s="8">
         <v>9965</v>
@@ -984,59 +1122,57 @@
         <v>0.543199781956937</v>
       </c>
       <c r="L8" s="18">
-        <v>0.226209933714701</v>
+        <v>0.184325404165588</v>
       </c>
       <c r="M8" s="20">
         <v>113.756352644296</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="5">
-        <v>66792</v>
-      </c>
-      <c r="F9" s="11">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>22740</v>
-      </c>
-      <c r="H9" s="13">
-        <v>0.340459935321595</v>
-      </c>
-      <c r="I9" s="15">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9">
-        <v>44052</v>
-      </c>
-      <c r="K9" s="17">
-        <v>0.659540064678405</v>
-      </c>
-      <c r="L9" s="19">
-        <v>1</v>
-      </c>
-      <c r="M9" s="21">
-        <v>50.778909948925</v>
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
+        <v>28421</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0.298499154527218</v>
+      </c>
+      <c r="G9" s="6">
+        <v>18411</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0.647795644066008</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0.447401035211781</v>
+      </c>
+      <c r="J9" s="8">
+        <v>10010</v>
+      </c>
+      <c r="K9" s="16">
+        <v>0.352204355933992</v>
+      </c>
+      <c r="L9" s="18">
+        <v>0.185157781806075</v>
+      </c>
+      <c r="M9" s="20">
+        <v>54.0732984193582</v>
       </c>
     </row>
     <row r="10">
@@ -1047,7 +1183,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TOTAL SUBREGIÓN OCCIDENTE</t>
+          <t>TOTAL PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1061,37 +1197,31 @@
         </is>
       </c>
       <c r="E10" s="5">
-        <v>225788</v>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>95213</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1</v>
       </c>
       <c r="G10" s="7">
-        <v>88348</v>
+        <v>41151</v>
       </c>
       <c r="H10" s="13">
-        <v>0.39128740234202</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>0.432199384537826</v>
+      </c>
+      <c r="I10" s="15">
+        <v>1</v>
       </c>
       <c r="J10" s="9">
-        <v>137440</v>
+        <v>54062</v>
       </c>
       <c r="K10" s="17">
-        <v>0.60871259765798</v>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>0.567800615462174</v>
+      </c>
+      <c r="L10" s="19">
+        <v>1</v>
       </c>
       <c r="M10" s="21">
-        <v>29.9211202882802</v>
+        <v>51.7194757126245</v>
       </c>
     </row>
     <row r="11">
@@ -1102,50 +1232,105 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>TOTAL SUBREGIÓN OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" s="5">
+        <v>225788</v>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" s="7">
+        <v>88348</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.39128740234202</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" s="9">
+        <v>137440</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0.60871259765798</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" s="21">
+        <v>29.9211202882802</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E11" s="5">
+      <c r="E12" s="5">
         <v>6928372</v>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G11" s="7">
+      <c r="G12" s="7">
         <v>5450720</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H12" s="13">
         <v>0.786724500358814</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="J11" s="9">
+      <c r="J12" s="9">
         <v>1477652</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K12" s="17">
         <v>0.213275499641186</v>
       </c>
-      <c r="L11" s="19" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="M11" s="21">
+      <c r="M12" s="21">
         <v>110.316120812453</v>
       </c>
     </row>
@@ -1158,32 +1343,32 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="112" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="112" t="inlineStr">
         <is>
           <t>Población total</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="112" t="inlineStr">
         <is>
           <t>Densidad poblacional (hab/km²)</t>
         </is>
@@ -1299,6 +1484,22 @@
       </c>
       <c r="D8">
         <v>113.756352644296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>28421</v>
+      </c>
+      <c r="D9">
+        <v>54.0732984193582</v>
       </c>
     </row>
   </sheetData>
@@ -1310,188 +1511,188 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Población masculina</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Población femenina</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>0 a 9</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>10 a 19</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>20 a 29</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>30 a 39</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>40 a 49</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="23" t="inlineStr">
         <is>
           <t>50 a 59</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>60 a 69</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="23" t="inlineStr">
         <is>
           <t>70 a 79</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="23" t="inlineStr">
         <is>
           <t>80 o más</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>Hombres 0 a 9</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="23" t="inlineStr">
         <is>
           <t>Hombres 10 a 19</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="23" t="inlineStr">
         <is>
           <t>Hombres 20 a 29</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="23" t="inlineStr">
         <is>
           <t>Hombres 30 a 39</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="23" t="inlineStr">
         <is>
           <t>Hombres 40 a 49</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="23" t="inlineStr">
         <is>
           <t>Hombres 50 a 59</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="23" t="inlineStr">
         <is>
           <t>Hombres 60 a 69</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="23" t="inlineStr">
         <is>
           <t>Hombres 70 a 79</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="23" t="inlineStr">
         <is>
           <t>Hombres 80 o más</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 0 a 9</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 10 a 19</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 20 a 29</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 30 a 39</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 40 a 49</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 50 a 59</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 60 a 69</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 70 a 79</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 80 o más</t>
         </is>
@@ -1516,91 +1717,91 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="25">
         <v>5256</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="27">
         <v>4849</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="29">
         <v>1743</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="31">
         <v>1640</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="33">
         <v>1571</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="35">
         <v>1531</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="37">
         <v>1234</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="39">
         <v>865</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="41">
         <v>736</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="43">
         <v>502</v>
       </c>
-      <c r="O2" s="42">
+      <c r="O2" s="45">
         <v>283</v>
       </c>
-      <c r="P2" s="44">
+      <c r="P2" s="47">
         <v>844</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="Q2" s="49">
         <v>816</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="51">
         <v>860</v>
       </c>
-      <c r="S2" s="50">
+      <c r="S2" s="53">
         <v>815</v>
       </c>
-      <c r="T2" s="52">
+      <c r="T2" s="55">
         <v>680</v>
       </c>
-      <c r="U2" s="54">
+      <c r="U2" s="57">
         <v>478</v>
       </c>
-      <c r="V2" s="56">
+      <c r="V2" s="59">
         <v>392</v>
       </c>
-      <c r="W2" s="58">
+      <c r="W2" s="61">
         <v>240</v>
       </c>
-      <c r="X2" s="60">
+      <c r="X2" s="63">
         <v>131</v>
       </c>
-      <c r="Y2" s="62">
+      <c r="Y2" s="65">
         <v>899</v>
       </c>
-      <c r="Z2" s="64">
+      <c r="Z2" s="67">
         <v>824</v>
       </c>
-      <c r="AA2" s="66">
+      <c r="AA2" s="69">
         <v>711</v>
       </c>
-      <c r="AB2" s="68">
+      <c r="AB2" s="71">
         <v>716</v>
       </c>
-      <c r="AC2" s="70">
+      <c r="AC2" s="73">
         <v>554</v>
       </c>
-      <c r="AD2" s="72">
+      <c r="AD2" s="75">
         <v>387</v>
       </c>
-      <c r="AE2" s="74">
+      <c r="AE2" s="77">
         <v>344</v>
       </c>
-      <c r="AF2" s="76">
+      <c r="AF2" s="79">
         <v>262</v>
       </c>
-      <c r="AG2" s="78">
+      <c r="AG2" s="81">
         <v>152</v>
       </c>
     </row>
@@ -1623,91 +1824,91 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="25">
         <v>6551</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="27">
         <v>6363</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="29">
         <v>1395</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="31">
         <v>1595</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="33">
         <v>1371</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="35">
         <v>1555</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="37">
         <v>1803</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="39">
         <v>1795</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="41">
         <v>1821</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="43">
         <v>1094</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="45">
         <v>485</v>
       </c>
-      <c r="P3" s="44">
+      <c r="P3" s="47">
         <v>666</v>
       </c>
-      <c r="Q3" s="46">
+      <c r="Q3" s="49">
         <v>859</v>
       </c>
-      <c r="R3" s="48">
+      <c r="R3" s="51">
         <v>711</v>
       </c>
-      <c r="S3" s="50">
+      <c r="S3" s="53">
         <v>776</v>
       </c>
-      <c r="T3" s="52">
+      <c r="T3" s="55">
         <v>907</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="57">
         <v>915</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="59">
         <v>924</v>
       </c>
-      <c r="W3" s="58">
+      <c r="W3" s="61">
         <v>556</v>
       </c>
-      <c r="X3" s="60">
+      <c r="X3" s="63">
         <v>237</v>
       </c>
-      <c r="Y3" s="62">
+      <c r="Y3" s="65">
         <v>729</v>
       </c>
-      <c r="Z3" s="64">
+      <c r="Z3" s="67">
         <v>736</v>
       </c>
-      <c r="AA3" s="66">
+      <c r="AA3" s="69">
         <v>660</v>
       </c>
-      <c r="AB3" s="68">
+      <c r="AB3" s="71">
         <v>779</v>
       </c>
-      <c r="AC3" s="70">
+      <c r="AC3" s="73">
         <v>896</v>
       </c>
-      <c r="AD3" s="72">
+      <c r="AD3" s="75">
         <v>880</v>
       </c>
-      <c r="AE3" s="74">
+      <c r="AE3" s="77">
         <v>897</v>
       </c>
-      <c r="AF3" s="76">
+      <c r="AF3" s="79">
         <v>538</v>
       </c>
-      <c r="AG3" s="78">
+      <c r="AG3" s="81">
         <v>248</v>
       </c>
     </row>
@@ -1730,91 +1931,91 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>3060</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="27">
         <v>2928</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="29">
         <v>1003</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="31">
         <v>933</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>852</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>949</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>725</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>544</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="41">
         <v>498</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="43">
         <v>317</v>
       </c>
-      <c r="O4" s="42">
+      <c r="O4" s="45">
         <v>167</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="47">
         <v>518</v>
       </c>
-      <c r="Q4" s="46">
+      <c r="Q4" s="49">
         <v>458</v>
       </c>
-      <c r="R4" s="48">
+      <c r="R4" s="51">
         <v>421</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="53">
         <v>503</v>
       </c>
-      <c r="T4" s="52">
+      <c r="T4" s="55">
         <v>394</v>
       </c>
-      <c r="U4" s="54">
+      <c r="U4" s="57">
         <v>269</v>
       </c>
-      <c r="V4" s="56">
+      <c r="V4" s="59">
         <v>279</v>
       </c>
-      <c r="W4" s="58">
+      <c r="W4" s="61">
         <v>147</v>
       </c>
-      <c r="X4" s="60">
+      <c r="X4" s="63">
         <v>71</v>
       </c>
-      <c r="Y4" s="62">
+      <c r="Y4" s="65">
         <v>485</v>
       </c>
-      <c r="Z4" s="64">
+      <c r="Z4" s="67">
         <v>475</v>
       </c>
-      <c r="AA4" s="66">
+      <c r="AA4" s="69">
         <v>431</v>
       </c>
-      <c r="AB4" s="68">
+      <c r="AB4" s="71">
         <v>446</v>
       </c>
-      <c r="AC4" s="70">
+      <c r="AC4" s="73">
         <v>331</v>
       </c>
-      <c r="AD4" s="72">
+      <c r="AD4" s="75">
         <v>275</v>
       </c>
-      <c r="AE4" s="74">
+      <c r="AE4" s="77">
         <v>219</v>
       </c>
-      <c r="AF4" s="76">
+      <c r="AF4" s="79">
         <v>170</v>
       </c>
-      <c r="AG4" s="78">
+      <c r="AG4" s="81">
         <v>96</v>
       </c>
     </row>
@@ -1837,91 +2038,91 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="25">
         <v>2998</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="27">
         <v>2756</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="29">
         <v>605</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="31">
         <v>729</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="33">
         <v>679</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="35">
         <v>749</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="37">
         <v>823</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="39">
         <v>799</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="41">
         <v>760</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="43">
         <v>404</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>206</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>301</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="49">
         <v>396</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="51">
         <v>358</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="53">
         <v>401</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="55">
         <v>438</v>
       </c>
-      <c r="U5" s="54">
+      <c r="U5" s="57">
         <v>414</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="59">
         <v>405</v>
       </c>
-      <c r="W5" s="58">
+      <c r="W5" s="61">
         <v>181</v>
       </c>
-      <c r="X5" s="60">
+      <c r="X5" s="63">
         <v>104</v>
       </c>
-      <c r="Y5" s="62">
+      <c r="Y5" s="65">
         <v>304</v>
       </c>
-      <c r="Z5" s="64">
+      <c r="Z5" s="67">
         <v>333</v>
       </c>
-      <c r="AA5" s="66">
+      <c r="AA5" s="69">
         <v>321</v>
       </c>
-      <c r="AB5" s="68">
+      <c r="AB5" s="71">
         <v>348</v>
       </c>
-      <c r="AC5" s="70">
+      <c r="AC5" s="73">
         <v>385</v>
       </c>
-      <c r="AD5" s="72">
+      <c r="AD5" s="75">
         <v>385</v>
       </c>
-      <c r="AE5" s="74">
+      <c r="AE5" s="77">
         <v>355</v>
       </c>
-      <c r="AF5" s="76">
+      <c r="AF5" s="79">
         <v>223</v>
       </c>
-      <c r="AG5" s="78">
+      <c r="AG5" s="81">
         <v>102</v>
       </c>
     </row>
@@ -1944,91 +2145,91 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <v>1678</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="27">
         <v>1672</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <v>474</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="31">
         <v>455</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="33">
         <v>393</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="35">
         <v>423</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="37">
         <v>480</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="39">
         <v>373</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="41">
         <v>372</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="43">
         <v>251</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="45">
         <v>129</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="47">
         <v>236</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="49">
         <v>227</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="51">
         <v>202</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="53">
         <v>204</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="55">
         <v>244</v>
       </c>
-      <c r="U6" s="54">
+      <c r="U6" s="57">
         <v>192</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="59">
         <v>195</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="61">
         <v>116</v>
       </c>
-      <c r="X6" s="60">
+      <c r="X6" s="63">
         <v>62</v>
       </c>
-      <c r="Y6" s="62">
+      <c r="Y6" s="65">
         <v>238</v>
       </c>
-      <c r="Z6" s="64">
+      <c r="Z6" s="67">
         <v>228</v>
       </c>
-      <c r="AA6" s="66">
+      <c r="AA6" s="69">
         <v>191</v>
       </c>
-      <c r="AB6" s="68">
+      <c r="AB6" s="71">
         <v>219</v>
       </c>
-      <c r="AC6" s="70">
+      <c r="AC6" s="73">
         <v>236</v>
       </c>
-      <c r="AD6" s="72">
+      <c r="AD6" s="75">
         <v>181</v>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="77">
         <v>177</v>
       </c>
-      <c r="AF6" s="76">
+      <c r="AF6" s="79">
         <v>135</v>
       </c>
-      <c r="AG6" s="78">
+      <c r="AG6" s="81">
         <v>67</v>
       </c>
     </row>
@@ -2051,91 +2252,91 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="25">
         <v>5103</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="27">
         <v>4628</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="29">
         <v>1830</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="31">
         <v>1587</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="33">
         <v>1474</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="35">
         <v>1416</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="37">
         <v>1137</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="39">
         <v>850</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="41">
         <v>725</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="43">
         <v>494</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="45">
         <v>218</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="47">
         <v>938</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="Q7" s="49">
         <v>825</v>
       </c>
-      <c r="R7" s="48">
+      <c r="R7" s="51">
         <v>785</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="53">
         <v>768</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="55">
         <v>615</v>
       </c>
-      <c r="U7" s="54">
+      <c r="U7" s="57">
         <v>446</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="59">
         <v>366</v>
       </c>
-      <c r="W7" s="58">
+      <c r="W7" s="61">
         <v>254</v>
       </c>
-      <c r="X7" s="60">
+      <c r="X7" s="63">
         <v>106</v>
       </c>
-      <c r="Y7" s="62">
+      <c r="Y7" s="65">
         <v>892</v>
       </c>
-      <c r="Z7" s="64">
+      <c r="Z7" s="67">
         <v>762</v>
       </c>
-      <c r="AA7" s="66">
+      <c r="AA7" s="69">
         <v>689</v>
       </c>
-      <c r="AB7" s="68">
+      <c r="AB7" s="71">
         <v>648</v>
       </c>
-      <c r="AC7" s="70">
+      <c r="AC7" s="73">
         <v>522</v>
       </c>
-      <c r="AD7" s="72">
+      <c r="AD7" s="75">
         <v>404</v>
       </c>
-      <c r="AE7" s="74">
+      <c r="AE7" s="77">
         <v>359</v>
       </c>
-      <c r="AF7" s="76">
+      <c r="AF7" s="79">
         <v>240</v>
       </c>
-      <c r="AG7" s="78">
+      <c r="AG7" s="81">
         <v>112</v>
       </c>
     </row>
@@ -2158,201 +2359,308 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="25">
         <v>8118</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="27">
         <v>8491</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="29">
         <v>2171</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="31">
         <v>2313</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="33">
         <v>2432</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="35">
         <v>2584</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="37">
         <v>2367</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="39">
         <v>1875</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="41">
         <v>1636</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="43">
         <v>855</v>
       </c>
-      <c r="O8" s="42">
+      <c r="O8" s="45">
         <v>376</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="47">
         <v>1011</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="49">
         <v>1169</v>
       </c>
-      <c r="R8" s="48">
+      <c r="R8" s="51">
         <v>1226</v>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="53">
         <v>1305</v>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="55">
         <v>1172</v>
       </c>
-      <c r="U8" s="54">
+      <c r="U8" s="57">
         <v>884</v>
       </c>
-      <c r="V8" s="56">
+      <c r="V8" s="59">
         <v>804</v>
       </c>
-      <c r="W8" s="58">
+      <c r="W8" s="61">
         <v>396</v>
       </c>
-      <c r="X8" s="60">
+      <c r="X8" s="63">
         <v>151</v>
       </c>
-      <c r="Y8" s="62">
+      <c r="Y8" s="65">
         <v>1160</v>
       </c>
-      <c r="Z8" s="64">
+      <c r="Z8" s="67">
         <v>1144</v>
       </c>
-      <c r="AA8" s="66">
+      <c r="AA8" s="69">
         <v>1206</v>
       </c>
-      <c r="AB8" s="68">
+      <c r="AB8" s="71">
         <v>1279</v>
       </c>
-      <c r="AC8" s="70">
+      <c r="AC8" s="73">
         <v>1195</v>
       </c>
-      <c r="AD8" s="72">
+      <c r="AD8" s="75">
         <v>991</v>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="77">
         <v>832</v>
       </c>
-      <c r="AF8" s="76">
+      <c r="AF8" s="79">
         <v>459</v>
       </c>
-      <c r="AG8" s="78">
+      <c r="AG8" s="81">
         <v>225</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="25">
+        <v>13944</v>
+      </c>
+      <c r="F9" s="27">
+        <v>14302</v>
+      </c>
+      <c r="G9" s="29">
+        <v>3798</v>
+      </c>
+      <c r="H9" s="31">
+        <v>4160</v>
+      </c>
+      <c r="I9" s="33">
+        <v>4314</v>
+      </c>
+      <c r="J9" s="35">
+        <v>4612</v>
+      </c>
+      <c r="K9" s="37">
+        <v>3727</v>
+      </c>
+      <c r="L9" s="39">
+        <v>2945</v>
+      </c>
+      <c r="M9" s="41">
+        <v>2498</v>
+      </c>
+      <c r="N9" s="43">
+        <v>1485</v>
+      </c>
+      <c r="O9" s="45">
+        <v>707</v>
+      </c>
+      <c r="P9" s="47">
+        <v>1926</v>
+      </c>
+      <c r="Q9" s="49">
+        <v>2138</v>
+      </c>
+      <c r="R9" s="51">
+        <v>2162</v>
+      </c>
+      <c r="S9" s="53">
+        <v>2314</v>
+      </c>
+      <c r="T9" s="55">
+        <v>1851</v>
+      </c>
+      <c r="U9" s="57">
+        <v>1414</v>
+      </c>
+      <c r="V9" s="59">
+        <v>1195</v>
+      </c>
+      <c r="W9" s="61">
+        <v>659</v>
+      </c>
+      <c r="X9" s="63">
+        <v>285</v>
+      </c>
+      <c r="Y9" s="65">
+        <v>1872</v>
+      </c>
+      <c r="Z9" s="67">
+        <v>2022</v>
+      </c>
+      <c r="AA9" s="69">
+        <v>2152</v>
+      </c>
+      <c r="AB9" s="71">
+        <v>2298</v>
+      </c>
+      <c r="AC9" s="73">
+        <v>1876</v>
+      </c>
+      <c r="AD9" s="75">
+        <v>1531</v>
+      </c>
+      <c r="AE9" s="77">
+        <v>1303</v>
+      </c>
+      <c r="AF9" s="79">
+        <v>826</v>
+      </c>
+      <c r="AG9" s="81">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E9" s="23">
-        <v>32764</v>
-      </c>
-      <c r="F9" s="25">
-        <v>31687</v>
-      </c>
-      <c r="G9" s="27">
-        <v>9221</v>
-      </c>
-      <c r="H9" s="29">
-        <v>9252</v>
-      </c>
-      <c r="I9" s="31">
-        <v>8772</v>
-      </c>
-      <c r="J9" s="33">
-        <v>9207</v>
-      </c>
-      <c r="K9" s="35">
-        <v>8569</v>
-      </c>
-      <c r="L9" s="37">
-        <v>7101</v>
-      </c>
-      <c r="M9" s="39">
-        <v>6548</v>
-      </c>
-      <c r="N9" s="41">
-        <v>3917</v>
-      </c>
-      <c r="O9" s="43">
-        <v>1864</v>
-      </c>
-      <c r="P9" s="45">
-        <v>4514</v>
-      </c>
-      <c r="Q9" s="47">
-        <v>4750</v>
-      </c>
-      <c r="R9" s="49">
-        <v>4563</v>
-      </c>
-      <c r="S9" s="51">
-        <v>4772</v>
-      </c>
-      <c r="T9" s="53">
-        <v>4450</v>
-      </c>
-      <c r="U9" s="55">
-        <v>3598</v>
-      </c>
-      <c r="V9" s="57">
-        <v>3365</v>
-      </c>
-      <c r="W9" s="59">
-        <v>1890</v>
-      </c>
-      <c r="X9" s="61">
-        <v>862</v>
-      </c>
-      <c r="Y9" s="63">
-        <v>4707</v>
-      </c>
-      <c r="Z9" s="65">
-        <v>4502</v>
-      </c>
-      <c r="AA9" s="67">
-        <v>4209</v>
-      </c>
-      <c r="AB9" s="69">
-        <v>4435</v>
-      </c>
-      <c r="AC9" s="71">
-        <v>4119</v>
-      </c>
-      <c r="AD9" s="73">
-        <v>3503</v>
-      </c>
-      <c r="AE9" s="75">
-        <v>3183</v>
-      </c>
-      <c r="AF9" s="77">
-        <v>2027</v>
-      </c>
-      <c r="AG9" s="79">
-        <v>1002</v>
+      <c r="E10" s="26">
+        <v>46708</v>
+      </c>
+      <c r="F10" s="28">
+        <v>45989</v>
+      </c>
+      <c r="G10" s="30">
+        <v>13019</v>
+      </c>
+      <c r="H10" s="32">
+        <v>13412</v>
+      </c>
+      <c r="I10" s="34">
+        <v>13086</v>
+      </c>
+      <c r="J10" s="36">
+        <v>13819</v>
+      </c>
+      <c r="K10" s="38">
+        <v>12296</v>
+      </c>
+      <c r="L10" s="40">
+        <v>10046</v>
+      </c>
+      <c r="M10" s="42">
+        <v>9046</v>
+      </c>
+      <c r="N10" s="44">
+        <v>5402</v>
+      </c>
+      <c r="O10" s="46">
+        <v>2571</v>
+      </c>
+      <c r="P10" s="48">
+        <v>6440</v>
+      </c>
+      <c r="Q10" s="50">
+        <v>6888</v>
+      </c>
+      <c r="R10" s="52">
+        <v>6725</v>
+      </c>
+      <c r="S10" s="54">
+        <v>7086</v>
+      </c>
+      <c r="T10" s="56">
+        <v>6301</v>
+      </c>
+      <c r="U10" s="58">
+        <v>5012</v>
+      </c>
+      <c r="V10" s="60">
+        <v>4560</v>
+      </c>
+      <c r="W10" s="62">
+        <v>2549</v>
+      </c>
+      <c r="X10" s="64">
+        <v>1147</v>
+      </c>
+      <c r="Y10" s="66">
+        <v>6579</v>
+      </c>
+      <c r="Z10" s="68">
+        <v>6524</v>
+      </c>
+      <c r="AA10" s="70">
+        <v>6361</v>
+      </c>
+      <c r="AB10" s="72">
+        <v>6733</v>
+      </c>
+      <c r="AC10" s="74">
+        <v>5995</v>
+      </c>
+      <c r="AD10" s="76">
+        <v>5034</v>
+      </c>
+      <c r="AE10" s="78">
+        <v>4486</v>
+      </c>
+      <c r="AF10" s="80">
+        <v>2853</v>
+      </c>
+      <c r="AG10" s="82">
+        <v>1424</v>
       </c>
     </row>
   </sheetData>
@@ -2364,50 +2672,50 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="71.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Natalidad</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Mortalidad</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Índice de Envejecimiento</t>
         </is>
@@ -2432,14 +2740,14 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="80">
+      <c r="E2" s="86">
         <v>10.0895803866101</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="88">
         <v>3.226401179941</v>
       </c>
-      <c r="G2" s="84">
-        <v>27.0473876063183</v>
+      <c r="G2" s="90">
+        <v>24.6293430328369</v>
       </c>
     </row>
     <row r="3">
@@ -2461,14 +2769,14 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="80">
+      <c r="E3" s="86">
         <v>2.78817812475106</v>
       </c>
-      <c r="F3" s="82">
+      <c r="F3" s="88">
         <v>5.62287162429714</v>
       </c>
-      <c r="G3" s="84">
-        <v>43.0249110320285</v>
+      <c r="G3" s="90">
+        <v>41.6482696533203</v>
       </c>
     </row>
     <row r="4">
@@ -2490,14 +2798,14 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="86">
         <v>11.3103894005494</v>
       </c>
-      <c r="F4" s="82">
+      <c r="F4" s="88">
         <v>4.264729110725</v>
       </c>
-      <c r="G4" s="84">
-        <v>28.6577992744861</v>
+      <c r="G4" s="90">
+        <v>28.9811325073242</v>
       </c>
     </row>
     <row r="5">
@@ -2519,14 +2827,14 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="86">
         <v>4.83091787439614</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="88">
         <v>7.99843932891143</v>
       </c>
-      <c r="G5" s="84">
-        <v>40.4018811457888</v>
+      <c r="G5" s="90">
+        <v>38.5217819213867</v>
       </c>
     </row>
     <row r="6">
@@ -2548,14 +2856,14 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="86">
         <v>5.04900504900505</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="88">
         <v>4.37190323520839</v>
       </c>
-      <c r="G6" s="84">
-        <v>37.9169503063308</v>
+      <c r="G6" s="90">
+        <v>37.1052627563477</v>
       </c>
     </row>
     <row r="7">
@@ -2577,14 +2885,14 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="86">
         <v>9.69872059430458</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="88">
         <v>4.17217869136054</v>
       </c>
-      <c r="G7" s="84">
-        <v>25.721271393643</v>
+      <c r="G7" s="90">
+        <v>25.1144847869873</v>
       </c>
     </row>
     <row r="8">
@@ -2606,107 +2914,136 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="86">
         <v>7.00894637871104</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="88">
         <v>4.5045045045045</v>
       </c>
-      <c r="G8" s="84">
-        <v>31.4925132828852</v>
+      <c r="G8" s="90">
+        <v>30.7646884918213</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="86">
+        <v>12.4811706477297</v>
+      </c>
+      <c r="F9" s="88">
+        <v>5.97227159616068</v>
+      </c>
+      <c r="G9" s="90">
+        <v>28.7996253967285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E9" s="81">
-        <v>7.26538912806343</v>
-      </c>
-      <c r="F9" s="83">
-        <v>4.68926390282652</v>
-      </c>
-      <c r="G9" s="85">
-        <v>32.8147459458113</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="E10" s="87">
+        <v>8.82229550188251</v>
+      </c>
+      <c r="F10" s="89">
+        <v>5.07224061453868</v>
+      </c>
+      <c r="G10" s="91">
+        <v>30.8434567791177</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E10" s="81">
+      <c r="E11" s="87">
         <v>8.34133878260628</v>
       </c>
-      <c r="F10" s="83">
+      <c r="F11" s="89">
         <v>4.90402610078376</v>
       </c>
-      <c r="G10" s="85">
-        <v>30.2492370183753</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="G11" s="91">
+        <v>28.6236767503016</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E11" s="81">
+      <c r="E12" s="87">
         <v>8.63819084562528</v>
       </c>
-      <c r="F11" s="83">
+      <c r="F12" s="89">
         <v>5.63888092494404</v>
       </c>
-      <c r="G11" s="85">
-        <v>32.052654940463</v>
+      <c r="G12" s="91">
+        <v>31.7311728877886</v>
       </c>
     </row>
   </sheetData>
@@ -2718,50 +3055,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="71.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - cabecera municipal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - centros poblados y rural</t>
         </is>
@@ -2786,13 +3123,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="86">
+      <c r="E2" s="95">
         <v>2.04869857262804</v>
       </c>
-      <c r="F2" s="88">
+      <c r="F2" s="97">
         <v>0.486111111111112</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="99">
         <v>2.68748521409983</v>
       </c>
     </row>
@@ -2815,13 +3152,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="95">
         <v>2.84208515467856</v>
       </c>
-      <c r="F3" s="88">
+      <c r="F3" s="97">
         <v>2.74330871630839</v>
       </c>
-      <c r="G3" s="90">
+      <c r="G3" s="99">
         <v>2.87308805291443</v>
       </c>
     </row>
@@ -2844,13 +3181,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="95">
         <v>0</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="97">
         <v>0</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="99">
         <v>0</v>
       </c>
     </row>
@@ -2873,13 +3210,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="95">
         <v>2.47426303094087</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="97">
         <v>2.16651890620574</v>
       </c>
-      <c r="G5" s="90">
+      <c r="G5" s="99">
         <v>2.75986879312295</v>
       </c>
     </row>
@@ -2902,13 +3239,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="95">
         <v>3.87352075338525</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="97">
         <v>8.8084871103739</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="99">
         <v>3.14394413714983</v>
       </c>
     </row>
@@ -2931,13 +3268,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="95">
         <v>0.11467889908257</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="97">
         <v>0.3003003003003</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="99">
         <v>0</v>
       </c>
     </row>
@@ -2960,106 +3297,135 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="95">
         <v>3.61220209002467</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="97">
         <v>0.620108558444838</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="99">
         <v>6.41866253960737</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="95">
+        <v>1.89919632990499</v>
+      </c>
+      <c r="F9" s="97">
+        <v>2.38236315000437</v>
+      </c>
+      <c r="G9" s="99">
+        <v>0.910491896700306</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E9" s="87">
-        <v>2.27146325823735</v>
-      </c>
-      <c r="F9" s="89">
-        <v>1.43394799728513</v>
-      </c>
-      <c r="G9" s="91">
-        <v>3.12011860158836</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="E10" s="96">
+        <v>2.1603418948717</v>
+      </c>
+      <c r="F10" s="98">
+        <v>1.71704911851262</v>
+      </c>
+      <c r="G10" s="100">
+        <v>2.46054689835851</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E10" s="87">
+      <c r="E11" s="96">
         <v>1.36963640191563</v>
       </c>
-      <c r="F10" s="89">
+      <c r="F11" s="98">
         <v>0.910301066336893</v>
       </c>
-      <c r="G10" s="91">
+      <c r="G11" s="100">
         <v>1.65713154831215</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E11" s="87">
+      <c r="E12" s="96">
         <v>2.43784156596946</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F12" s="98">
         <v>2.2991539975123</v>
       </c>
-      <c r="G11" s="91">
+      <c r="G12" s="100">
         <v>2.88568680338064</v>
       </c>
     </row>
@@ -3072,26 +3438,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="102" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="102" t="inlineStr">
         <is>
           <t>part_total_prov</t>
         </is>
@@ -3107,7 +3473,7 @@
         <v>11015</v>
       </c>
       <c r="C2">
-        <v>0.164914959875434</v>
+        <v>0.115687983783727</v>
       </c>
     </row>
     <row r="3">
@@ -3120,7 +3486,7 @@
         <v>12612</v>
       </c>
       <c r="C3">
-        <v>0.188825008983112</v>
+        <v>0.132460903448059</v>
       </c>
     </row>
     <row r="4">
@@ -3133,7 +3499,7 @@
         <v>6404</v>
       </c>
       <c r="C4">
-        <v>0.0958797460773745</v>
+        <v>0.0672597229369939</v>
       </c>
     </row>
     <row r="5">
@@ -3146,7 +3512,7 @@
         <v>5038</v>
       </c>
       <c r="C5">
-        <v>0.0754281949934124</v>
+        <v>0.0529129425603647</v>
       </c>
     </row>
     <row r="6">
@@ -3159,7 +3525,7 @@
         <v>3469</v>
       </c>
       <c r="C6">
-        <v>0.0519373577673973</v>
+        <v>0.0364341003854516</v>
       </c>
     </row>
     <row r="7">
@@ -3172,7 +3538,7 @@
         <v>9909</v>
       </c>
       <c r="C7">
-        <v>0.148356090549766</v>
+        <v>0.104071922951698</v>
       </c>
     </row>
     <row r="8">
@@ -3185,7 +3551,20 @@
         <v>18345</v>
       </c>
       <c r="C8">
-        <v>0.274658641753503</v>
+        <v>0.192673269406489</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>28421</v>
+      </c>
+      <c r="C9">
+        <v>0.298499154527218</v>
       </c>
     </row>
   </sheetData>
@@ -3197,38 +3576,38 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>habitantes_cabecera</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="104" t="inlineStr">
         <is>
           <t>pct_cabecera</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="104" t="inlineStr">
         <is>
           <t>habitantes_rural</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="104" t="inlineStr">
         <is>
           <t>pct_rural</t>
         </is>
@@ -3365,6 +3744,25 @@
       </c>
       <c r="E8">
         <v>0.543199781956937</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>18411</v>
+      </c>
+      <c r="C9">
+        <v>0.647795644066008</v>
+      </c>
+      <c r="D9">
+        <v>10010</v>
+      </c>
+      <c r="E9">
+        <v>0.352204355933992</v>
       </c>
     </row>
   </sheetData>
@@ -3376,25 +3774,26 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t>densidad_pob</t>
         </is>
@@ -3489,6 +3888,19 @@
       </c>
       <c r="C8">
         <v>113.756352644296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>28421</v>
+      </c>
+      <c r="C9">
+        <v>54.0732984193582</v>
       </c>
     </row>
   </sheetData>
@@ -3503,23 +3915,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>banda</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="108" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="108" t="inlineStr">
         <is>
           <t>personas</t>
         </is>
@@ -3537,7 +3949,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>4514</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="3">
@@ -3552,7 +3964,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>4750</v>
+        <v>6888</v>
       </c>
     </row>
     <row r="4">
@@ -3567,7 +3979,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>4563</v>
+        <v>6725</v>
       </c>
     </row>
     <row r="5">
@@ -3582,7 +3994,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>4772</v>
+        <v>7086</v>
       </c>
     </row>
     <row r="6">
@@ -3597,7 +4009,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>4450</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="7">
@@ -3612,7 +4024,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>3598</v>
+        <v>5012</v>
       </c>
     </row>
     <row r="8">
@@ -3627,7 +4039,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>3365</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="9">
@@ -3642,7 +4054,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>1890</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="10">
@@ -3657,7 +4069,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>862</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="11">
@@ -3672,7 +4084,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>4707</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="12">
@@ -3687,7 +4099,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>4502</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="13">
@@ -3702,7 +4114,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>4209</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="14">
@@ -3717,7 +4129,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>4435</v>
+        <v>6733</v>
       </c>
     </row>
     <row r="15">
@@ -3732,7 +4144,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>4119</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="16">
@@ -3747,7 +4159,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>3503</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="17">
@@ -3762,7 +4174,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>3183</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="18">
@@ -3777,7 +4189,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>2027</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="19">
@@ -3792,7 +4204,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>1002</v>
+        <v>1424</v>
       </c>
     </row>
   </sheetData>
@@ -3804,20 +4216,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="110" t="inlineStr">
         <is>
           <t>I_enve_T</t>
         </is>
@@ -3830,7 +4242,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>27.0473876063183</v>
+        <v>24.6293430328369</v>
       </c>
     </row>
     <row r="3">
@@ -3840,7 +4252,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>43.0249110320285</v>
+        <v>41.6482696533203</v>
       </c>
     </row>
     <row r="4">
@@ -3850,7 +4262,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>28.6577992744861</v>
+        <v>28.9811325073242</v>
       </c>
     </row>
     <row r="5">
@@ -3860,7 +4272,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>40.4018811457888</v>
+        <v>38.5217819213867</v>
       </c>
     </row>
     <row r="6">
@@ -3870,7 +4282,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>37.9169503063308</v>
+        <v>37.1052627563477</v>
       </c>
     </row>
     <row r="7">
@@ -3880,7 +4292,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>25.721271393643</v>
+        <v>25.1144847869873</v>
       </c>
     </row>
     <row r="8">
@@ -3890,7 +4302,17 @@
         </is>
       </c>
       <c r="B8">
-        <v>31.4925132828852</v>
+        <v>30.7646884918213</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>28.7996253967285</v>
       </c>
     </row>
   </sheetData>
